--- a/task281/golden/fy2028_relief_positions_by_unit.xlsx
+++ b/task281/golden/fy2028_relief_positions_by_unit.xlsx
@@ -161,7 +161,7 @@
     <t>People who worked more than 600 hours of overtime</t>
   </si>
   <si>
-    <t>Hours worked: overtime paid at time and a half, and compensatory time at one hour worked for each 1.5 hours credited (MOU 14.2), hour for hour for the Forensic Security Aides, whose unit the MOU does not cover; night differential and retroactive lines carry pay only, and a timesheet Central Payroll paid a second time on a later check is one piece of work. By the unit the piece was posted at in the offer log, else the line's work location (SL-0410 is Thornmere).</t>
+    <t>Hours worked: overtime paid at time and a half, and compensatory time at one hour worked for each 1.5 hours credited (CTE, MOU 14.2) or each hour credited (CTS, the Forensic Security Aides); night differential and retroactive lines carry pay only, and a timesheet Central Payroll paid a second time on a later check is one piece of work. By the unit whose post the piece was accepted at in the offer log, else the employee's own unit (the home timekeeper; SL-0410 is Thornmere).</t>
   </si>
   <si>
     <t>People: everyone with an overtime or compensatory time piece dated in FY2026 at the unit, counted once at each unit they worked at; an employee's two records are one person. The all-units line is not given for people, since one person can work at more than one unit.</t>
